--- a/MsPFM/AIC8820/MsTables/20241021/WF_MEASURE_TABLE_20241021.xlsx
+++ b/MsPFM/AIC8820/MsTables/20241021/WF_MEASURE_TABLE_20241021.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>TEST_ENABLE</t>
   </si>
@@ -46,7 +46,10 @@
     <t>R_EVM_PEAK</t>
   </si>
   <si>
-    <t>R_MASK</t>
+    <t>R_MASK_AVG</t>
+  </si>
+  <si>
+    <t>R_MASK_MAX</t>
   </si>
   <si>
     <t>Y</t>
@@ -1044,7 +1047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -1053,9 +1056,10 @@
     <col min="7" max="7" width="27.25" customWidth="1"/>
     <col min="9" max="9" width="14.5" customWidth="1"/>
     <col min="10" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1089,40 +1093,46 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1">
         <v>40000</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:11">
